--- a/operations/vendor-source/vevor/2026-09-10/VEVOR_A_TIER_RUN_COMPLETE_2026-09-10_PUBLIC_SAFE.xlsx
+++ b/operations/vendor-source/vevor/2026-09-10/VEVOR_A_TIER_RUN_COMPLETE_2026-09-10_PUBLIC_SAFE.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>381</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>287</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2462</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">

--- a/operations/vendor-source/vevor/2026-09-10/VEVOR_A_TIER_RUN_COMPLETE_2026-09-10_PUBLIC_SAFE.xlsx
+++ b/operations/vendor-source/vevor/2026-09-10/VEVOR_A_TIER_RUN_COMPLETE_2026-09-10_PUBLIC_SAFE.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>395</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>143</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>286</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>561</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>529</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>878</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">

--- a/operations/vendor-source/vevor/2026-09-10/VEVOR_A_TIER_RUN_COMPLETE_2026-09-10_PUBLIC_SAFE.xlsx
+++ b/operations/vendor-source/vevor/2026-09-10/VEVOR_A_TIER_RUN_COMPLETE_2026-09-10_PUBLIC_SAFE.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>314</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2442</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>526</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">

--- a/operations/vendor-source/vevor/2026-09-10/VEVOR_A_TIER_RUN_COMPLETE_2026-09-10_PUBLIC_SAFE.xlsx
+++ b/operations/vendor-source/vevor/2026-09-10/VEVOR_A_TIER_RUN_COMPLETE_2026-09-10_PUBLIC_SAFE.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
